--- a/reference/verification/Labourmax_statutory_verification.xlsx
+++ b/reference/verification/Labourmax_statutory_verification.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="506">
   <si>
     <t xml:space="preserve">Labourmax-HR — statutory data verification</t>
   </si>
@@ -195,7 +195,7 @@
     <t xml:space="preserve">effective_from is the start of this reference data, not the provision's commencement. The rule itself is older. DERIVED, not transcribed. BCEA s10(1)(b) caps the whole day at 12 hours including overtime; three is that cap less a nine-hour ordinary day. On an eight-hour six-day week the same cap allows four. ZERO MEANS THERE IS NO STATUTORY FIGURE, not that the amount is nil. BCEA s17(2) requires night work to be compensated by an allowance or by reduced hours, and deliberately sets no amount - the employer sets it. A calculator must read the employer's own setting, not this column. VERIFY THE STANDBY ALLOWANCE. R20 per shift is the figure in the determination as published and no later amendment was found. It may well have escalated - it is the one figure in this load most likely to be stale. SD7 also caps standby at five shifts a month and fifty a year, which this table has no column for. Overtime in this sector is 15 hours a week, not the Act's 10. The 20:00-06:00 standby window comes from a secondary summary rather than the gazette text.</t>
   </si>
   <si>
-    <t xml:space="preserve">Query</t>
+    <t xml:space="preserve">Labour Guide consolidated SD7 — standby 20:00-06:00 at R20 per shift, work beyond three hours attracts overtime, accommodation deduction not more than 10%. Second independent source; matches all four loaded columns.</t>
   </si>
   <si>
     <t xml:space="preserve">3606</t>
@@ -228,6 +228,30 @@
     <t xml:space="preserve">VERIFY THE COIDA FLAG. Overtime is plainly taxable and plainly in the UIF and SDL bases. COIDA's definition of earnings treats overtime differently depending on whether it is regular or casual, and this row takes the inclusive reading, which over-declares rather than under-declares on the Return of Earnings. A wrong answer here costs an assessment, not a payslip. One for the labour law review (O-06). COIDA base: Compensation for Occupational Injuries and Diseases Act 130 of 1993, s1 definition of earnings.</t>
   </si>
   <si>
+    <t xml:space="preserve">3901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gratuities / Severance Benefits (Subject to PAYE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAYE True / UIF False / SDL False / COIDA False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SARS PAYE-AE-06-G06, Guide for Codes Applicable to Employees Tax Certificates 2026, revision 13, effective 19 September 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The guide: 'Severance benefits, as defined, paid/payable by an employer after 1 March 2011, if employee: is 55 years or older; became permanently incapable to be employed due to ill health, etc.; or services terminated due to reduction of personnel or employer ceased trading.' THE THIRD LIMB IS THE ONE THIS PRODUCT USES: 'reduction of personnel' is dismissal for operational requirements, which is the only ground on which BCEA s41 severance is due. It matches EmployeeEngagement.SEVERANCE_REASONS exactly. A lump sum on resignation, or on retirement below 55, is NOT a severance benefit and goes to 3907 - the guide says MUST. 3951 is for foreign services income only and is not loaded. UIF base False: UICA 4 of 2002 s1 excludes paragraph (d) gross income amounts, and the guide places this code in paragraph (d). SDL base False: SDLA 9 of 1999 s3 excludes paragraph (d) likewise. COIDA base False is a READING, NOT A CITATION - VERIFY. No source was found naming termination lump sums in the COIDA earnings definition; False is the reading that a severance benefit is not earnings in respect of employment during the assessment period.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other lump sums (Subject to PAYE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loaded because leaving it out is the trap. The guide's note on 3901 says a lump sum under paragraph (d) of 'gross income' which is NOT a severance benefit MUST be reflected under 3907 - so without this code the only one available would be 3901, which is exactly the misfiling that note exists to prevent. The guide's examples: 'A lump sum payment paid/payable by an employer due to normal termination of service (e.g., resignation or retirement), which is NOT a severance benefit' and 'Gratuity paid to an employee due to normal termination of service (e.g., resignation or a lump sum paid upon retirement where employee is below 55 years of age).' 3957 is for foreign services income only and is not loaded. Base flags derived exactly as for 3901, same paragraph (d), same two statutes. COIDA base False is a READING - VERIFY.</t>
+  </si>
+  <si>
     <t xml:space="preserve">4001</t>
   </si>
   <si>
@@ -252,6 +276,9 @@
     <t xml:space="preserve">The contract cleaning sector has a national provident fund under SD1 clause 32, so this code carries real traffic there. Its contribution rates are not loaded - they are not in this table's scope and were not researched. A total or a deduction, not a pay line. All four base flags are False because nothing is ever calculated FROM this code - it is calculated INTO it. A calculator that reads a base flag here has asked the wrong question. VERIFY THE WORDING before P8 generates an IRP5. The description here is the conventional one; it was not transcribed character for character from the SARS guide, which gives full wording only for selected codes.</t>
   </si>
   <si>
+    <t xml:space="preserve">SARS PAYE-AE-06-G06 rev 13 (2026 guide), s3 valid-codes table — the flags say whether the amount is IN the base the levy is computed on. Nothing is ever computed from a deduction or a total, so all four are false by construction.</t>
+  </si>
+  <si>
     <t xml:space="preserve">4005</t>
   </si>
   <si>
@@ -1422,7 +1449,7 @@
     <t xml:space="preserve">Area C has no gazetted figure. Its wages come from the BCCCI collective agreement, which is extended by the Minister and runs on its own cycle. NOT YET LOADED - the agreement is needed before any KwaZulu-Natal contract cleaning employer can be onboarded.</t>
   </si>
   <si>
-    <t xml:space="preserve">The 7 reference data versions</t>
+    <t xml:space="preserve">The 8 reference data versions</t>
   </si>
   <si>
     <t xml:space="preserve">A version that is not verified is not in force, and every payroll run stays blocked. That is deliberate.</t>
@@ -1510,6 +1537,15 @@
   </si>
   <si>
     <t xml:space="preserve">Rate derivation constants from the Basic Conditions of Employment Act. Researched 13 September 2026. NOT verified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REF-2026.03.01-LUMPSUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4a348c5d19be</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Termination lump sum source codes 3901 and 3907, from SARS's 2026 code guide. Researched 13 September 2026. NOT verified.</t>
   </si>
 </sst>
 </file>
@@ -2072,7 +2108,7 @@
       </c>
       <c r="D3" s="6" t="str">
         <f aca="false">COUNTA(Priority!G5:G2000)&amp;" of "&amp;COUNTA(Priority!A5:A2000)&amp;" checked"</f>
-        <v>20 of 20 checked</v>
+        <v>20 of 22 checked</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2104,7 +2140,7 @@
       </c>
       <c r="D6" s="6" t="str">
         <f aca="false">COUNTA('SARS source codes'!G5:G2000)&amp;" of "&amp;COUNTA('SARS source codes'!A5:A2000)&amp;" checked"</f>
-        <v>10 of 19 checked</v>
+        <v>10 of 21 checked</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2255,7 +2291,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
@@ -2375,10 +2411,12 @@
         <v>54</v>
       </c>
       <c r="G7" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
@@ -2430,7 +2468,7 @@
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
     </row>
-    <row r="10" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
         <v>66</v>
       </c>
@@ -2438,24 +2476,22 @@
         <v>67</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>60</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>44</v>
-      </c>
+      <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
     </row>
-    <row r="11" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
         <v>71</v>
       </c>
@@ -2463,20 +2499,18 @@
         <v>72</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>60</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="G11" s="13" t="s">
-        <v>55</v>
-      </c>
+      <c r="G11" s="13"/>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
     </row>
@@ -2488,210 +2522,228 @@
         <v>75</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
     </row>
-    <row r="13" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="D13" s="11" t="s">
         <v>77</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>69</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
+      <c r="I13" s="13" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-    </row>
-    <row r="15" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I14" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-    </row>
-    <row r="16" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I15" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-    </row>
-    <row r="17" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I16" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-    </row>
-    <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I17" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" s="12"/>
+        <v>77</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="F18" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>44</v>
       </c>
       <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-    </row>
-    <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I18" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" s="12"/>
+        <v>77</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="F19" s="12" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>44</v>
       </c>
       <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
+      <c r="I19" s="13" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>44</v>
@@ -2701,20 +2753,20 @@
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="12" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>44</v>
@@ -2724,20 +2776,20 @@
     </row>
     <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="12" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>44</v>
@@ -2747,20 +2799,20 @@
     </row>
     <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="12" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>44</v>
@@ -2770,20 +2822,20 @@
     </row>
     <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="12" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>44</v>
@@ -2791,8 +2843,54 @@
       <c r="H24" s="13"/>
       <c r="I24" s="13"/>
     </row>
+    <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+    </row>
+    <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="G5:G24">
+  <conditionalFormatting sqref="G5:G26">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Y"</formula>
     </cfRule>
@@ -2804,7 +2902,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Y if the loaded figure matches the source, N if it does not, Query if you could not find the document." errorStyle="stop" errorTitle="One of three answers" operator="between" prompt="Y, N or Query." promptTitle="Does the loaded value agree?" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G5:G24" type="list">
+    <dataValidation allowBlank="true" error="Y if the loaded figure matches the source, N if it does not, Query if you could not find the document." errorStyle="stop" errorTitle="One of three answers" operator="between" prompt="Y, N or Query." promptTitle="Does the loaded value agree?" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G5:G26" type="list">
       <formula1>"Y,N,Query"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2840,12 +2938,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2865,7 +2963,7 @@
         <v>33</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>35</v>
@@ -2879,22 +2977,22 @@
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
@@ -2902,22 +3000,22 @@
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
@@ -2925,22 +3023,22 @@
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
@@ -2948,22 +3046,22 @@
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>51</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
@@ -2971,19 +3069,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="13"/>
@@ -2992,22 +3090,22 @@
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
@@ -3015,22 +3113,22 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
@@ -3038,22 +3136,22 @@
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
@@ -3061,22 +3159,22 @@
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
@@ -3084,22 +3182,22 @@
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D14" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>130</v>
-      </c>
       <c r="F14" s="15" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
@@ -3107,22 +3205,22 @@
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B15" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>140</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>131</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
@@ -3130,22 +3228,22 @@
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
@@ -3153,22 +3251,22 @@
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
@@ -3176,22 +3274,22 @@
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
@@ -3199,22 +3297,22 @@
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
@@ -3222,22 +3320,22 @@
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
@@ -3248,16 +3346,16 @@
         <v>38</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F21" s="15"/>
       <c r="G21" s="13"/>
@@ -3269,16 +3367,16 @@
         <v>38</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="F22" s="15"/>
       <c r="G22" s="13"/>
@@ -3311,19 +3409,19 @@
         <v>38</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
@@ -3334,19 +3432,19 @@
         <v>38</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="G25" s="13"/>
       <c r="H25" s="13"/>
@@ -3357,16 +3455,16 @@
         <v>38</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>40</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="13"/>
@@ -3378,16 +3476,16 @@
         <v>38</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>40</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F27" s="15"/>
       <c r="G27" s="13"/>
@@ -3399,16 +3497,16 @@
         <v>38</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="13"/>
@@ -3420,16 +3518,16 @@
         <v>38</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="F29" s="15"/>
       <c r="G29" s="13"/>
@@ -3462,16 +3560,16 @@
         <v>38</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>40</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="13"/>
@@ -3527,20 +3625,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>31</v>
@@ -3552,7 +3650,7 @@
         <v>33</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>35</v>
@@ -3566,22 +3664,22 @@
     </row>
     <row r="5" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
@@ -3589,22 +3687,22 @@
     </row>
     <row r="6" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
@@ -3612,22 +3710,22 @@
     </row>
     <row r="7" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
@@ -3635,22 +3733,22 @@
     </row>
     <row r="8" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
@@ -3658,22 +3756,22 @@
     </row>
     <row r="9" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="D9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="E9" s="17" t="s">
-        <v>196</v>
-      </c>
       <c r="F9" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
@@ -3681,22 +3779,22 @@
     </row>
     <row r="10" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C10" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="F10" s="17" t="s">
         <v>206</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>197</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
@@ -3704,22 +3802,22 @@
     </row>
     <row r="11" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
@@ -3727,22 +3825,22 @@
     </row>
     <row r="12" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
@@ -3750,22 +3848,22 @@
     </row>
     <row r="13" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
@@ -3773,22 +3871,22 @@
     </row>
     <row r="14" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
@@ -3796,22 +3894,22 @@
     </row>
     <row r="15" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
@@ -3819,22 +3917,22 @@
     </row>
     <row r="16" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="13"/>
@@ -3842,22 +3940,22 @@
     </row>
     <row r="17" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="13"/>
@@ -3865,22 +3963,22 @@
     </row>
     <row r="18" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
@@ -3888,22 +3986,22 @@
     </row>
     <row r="19" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
@@ -3911,22 +4009,22 @@
     </row>
     <row r="20" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
@@ -3934,22 +4032,22 @@
     </row>
     <row r="21" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
@@ -3957,22 +4055,22 @@
     </row>
     <row r="22" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
@@ -3980,22 +4078,22 @@
     </row>
     <row r="23" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
@@ -4003,22 +4101,22 @@
     </row>
     <row r="24" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G24" s="13"/>
       <c r="H24" s="13"/>
@@ -4026,22 +4124,22 @@
     </row>
     <row r="25" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G25" s="13"/>
       <c r="H25" s="13"/>
@@ -4049,22 +4147,22 @@
     </row>
     <row r="26" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G26" s="13"/>
       <c r="H26" s="13"/>
@@ -4072,22 +4170,22 @@
     </row>
     <row r="27" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B27" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
@@ -4095,22 +4193,22 @@
     </row>
     <row r="28" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G28" s="13"/>
       <c r="H28" s="13"/>
@@ -4118,22 +4216,22 @@
     </row>
     <row r="29" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B29" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
@@ -4141,22 +4239,22 @@
     </row>
     <row r="30" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B30" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G30" s="13"/>
       <c r="H30" s="13"/>
@@ -4164,22 +4262,22 @@
     </row>
     <row r="31" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B31" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G31" s="13"/>
       <c r="H31" s="13"/>
@@ -4187,22 +4285,22 @@
     </row>
     <row r="32" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G32" s="13"/>
       <c r="H32" s="13"/>
@@ -4210,22 +4308,22 @@
     </row>
     <row r="33" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G33" s="13"/>
       <c r="H33" s="13"/>
@@ -4233,22 +4331,22 @@
     </row>
     <row r="34" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B34" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
@@ -4256,22 +4354,22 @@
     </row>
     <row r="35" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
@@ -4279,22 +4377,22 @@
     </row>
     <row r="36" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B36" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G36" s="13"/>
       <c r="H36" s="13"/>
@@ -4302,22 +4400,22 @@
     </row>
     <row r="37" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B37" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G37" s="13"/>
       <c r="H37" s="13"/>
@@ -4325,22 +4423,22 @@
     </row>
     <row r="38" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B38" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
@@ -4348,22 +4446,22 @@
     </row>
     <row r="39" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B39" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
@@ -4371,22 +4469,22 @@
     </row>
     <row r="40" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B40" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G40" s="13"/>
       <c r="H40" s="13"/>
@@ -4394,22 +4492,22 @@
     </row>
     <row r="41" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B41" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G41" s="13"/>
       <c r="H41" s="13"/>
@@ -4417,22 +4515,22 @@
     </row>
     <row r="42" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B42" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G42" s="13"/>
       <c r="H42" s="13"/>
@@ -4440,22 +4538,22 @@
     </row>
     <row r="43" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B43" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G43" s="13"/>
       <c r="H43" s="13"/>
@@ -4463,22 +4561,22 @@
     </row>
     <row r="44" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B44" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G44" s="13"/>
       <c r="H44" s="13"/>
@@ -4486,22 +4584,22 @@
     </row>
     <row r="45" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B45" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G45" s="13"/>
       <c r="H45" s="13"/>
@@ -4509,22 +4607,22 @@
     </row>
     <row r="46" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B46" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="G46" s="13"/>
       <c r="H46" s="13"/>
@@ -4532,22 +4630,22 @@
     </row>
     <row r="47" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G47" s="13"/>
       <c r="H47" s="13"/>
@@ -4555,22 +4653,22 @@
     </row>
     <row r="48" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G48" s="13"/>
       <c r="H48" s="13"/>
@@ -4578,22 +4676,22 @@
     </row>
     <row r="49" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G49" s="13"/>
       <c r="H49" s="13"/>
@@ -4601,22 +4699,22 @@
     </row>
     <row r="50" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G50" s="13"/>
       <c r="H50" s="13"/>
@@ -4624,22 +4722,22 @@
     </row>
     <row r="51" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G51" s="13"/>
       <c r="H51" s="13"/>
@@ -4647,22 +4745,22 @@
     </row>
     <row r="52" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G52" s="13"/>
       <c r="H52" s="13"/>
@@ -4670,22 +4768,22 @@
     </row>
     <row r="53" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G53" s="13"/>
       <c r="H53" s="13"/>
@@ -4693,22 +4791,22 @@
     </row>
     <row r="54" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G54" s="13"/>
       <c r="H54" s="13"/>
@@ -4716,22 +4814,22 @@
     </row>
     <row r="55" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C55" s="16" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F55" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G55" s="13"/>
       <c r="H55" s="13"/>
@@ -4739,22 +4837,22 @@
     </row>
     <row r="56" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F56" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G56" s="13"/>
       <c r="H56" s="13"/>
@@ -4762,22 +4860,22 @@
     </row>
     <row r="57" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C57" s="16" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F57" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G57" s="13"/>
       <c r="H57" s="13"/>
@@ -4785,22 +4883,22 @@
     </row>
     <row r="58" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F58" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
@@ -4808,22 +4906,22 @@
     </row>
     <row r="59" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F59" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G59" s="13"/>
       <c r="H59" s="13"/>
@@ -4831,22 +4929,22 @@
     </row>
     <row r="60" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F60" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G60" s="13"/>
       <c r="H60" s="13"/>
@@ -4854,22 +4952,22 @@
     </row>
     <row r="61" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F61" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G61" s="13"/>
       <c r="H61" s="13"/>
@@ -4877,22 +4975,22 @@
     </row>
     <row r="62" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F62" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G62" s="13"/>
       <c r="H62" s="13"/>
@@ -4900,22 +4998,22 @@
     </row>
     <row r="63" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B63" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C63" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="C63" s="16" t="s">
-        <v>226</v>
-      </c>
       <c r="D63" s="16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G63" s="13"/>
       <c r="H63" s="13"/>
@@ -4923,22 +5021,22 @@
     </row>
     <row r="64" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G64" s="13"/>
       <c r="H64" s="13"/>
@@ -4946,22 +5044,22 @@
     </row>
     <row r="65" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G65" s="13"/>
       <c r="H65" s="13"/>
@@ -4969,22 +5067,22 @@
     </row>
     <row r="66" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F66" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G66" s="13"/>
       <c r="H66" s="13"/>
@@ -4992,22 +5090,22 @@
     </row>
     <row r="67" customFormat="false" ht="113.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F67" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="G67" s="13"/>
       <c r="H67" s="13"/>
@@ -5021,10 +5119,10 @@
         <v>51</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>53</v>
@@ -5046,10 +5144,10 @@
         <v>51</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>53</v>
@@ -5071,10 +5169,10 @@
         <v>51</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="E70" s="12" t="s">
         <v>53</v>
@@ -5096,10 +5194,10 @@
         <v>51</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E71" s="12" t="s">
         <v>53</v>
@@ -5121,10 +5219,10 @@
         <v>51</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>53</v>
@@ -5146,10 +5244,10 @@
         <v>51</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E73" s="12" t="s">
         <v>53</v>
@@ -5171,10 +5269,10 @@
         <v>51</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>53</v>
@@ -5196,10 +5294,10 @@
         <v>51</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E75" s="12" t="s">
         <v>53</v>
@@ -5221,10 +5319,10 @@
         <v>51</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>53</v>
@@ -5246,10 +5344,10 @@
         <v>51</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E77" s="12" t="s">
         <v>53</v>
@@ -5271,10 +5369,10 @@
         <v>51</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>53</v>
@@ -5296,10 +5394,10 @@
         <v>51</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="E79" s="12" t="s">
         <v>53</v>
@@ -5321,10 +5419,10 @@
         <v>51</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="E80" s="12" t="s">
         <v>53</v>
@@ -5346,10 +5444,10 @@
         <v>51</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="E81" s="12" t="s">
         <v>53</v>
@@ -5362,7 +5460,7 @@
       </c>
       <c r="H81" s="13"/>
       <c r="I81" s="13" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5373,10 +5471,10 @@
         <v>51</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="E82" s="12" t="s">
         <v>53</v>
@@ -5398,10 +5496,10 @@
         <v>51</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="E83" s="12" t="s">
         <v>53</v>
@@ -5423,10 +5521,10 @@
         <v>51</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="E84" s="12" t="s">
         <v>53</v>
@@ -5448,10 +5546,10 @@
         <v>51</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="E85" s="12" t="s">
         <v>53</v>
@@ -5473,10 +5571,10 @@
         <v>51</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E86" s="12" t="s">
         <v>53</v>
@@ -5498,10 +5596,10 @@
         <v>51</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="E87" s="12" t="s">
         <v>53</v>
@@ -5523,10 +5621,10 @@
         <v>51</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="E88" s="12" t="s">
         <v>53</v>
@@ -5548,10 +5646,10 @@
         <v>51</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E89" s="12" t="s">
         <v>53</v>
@@ -5573,10 +5671,10 @@
         <v>51</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E90" s="12" t="s">
         <v>53</v>
@@ -5598,10 +5696,10 @@
         <v>51</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="E91" s="12" t="s">
         <v>53</v>
@@ -5620,19 +5718,19 @@
         <v>50</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D92" s="16" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="E92" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F92" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G92" s="13"/>
       <c r="H92" s="13"/>
@@ -5643,19 +5741,19 @@
         <v>50</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C93" s="16" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="E93" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F93" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G93" s="13"/>
       <c r="H93" s="13"/>
@@ -5666,19 +5764,19 @@
         <v>50</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C94" s="16" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D94" s="16" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F94" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G94" s="13"/>
       <c r="H94" s="13"/>
@@ -5689,19 +5787,19 @@
         <v>50</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F95" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G95" s="13"/>
       <c r="H95" s="13"/>
@@ -5712,19 +5810,19 @@
         <v>50</v>
       </c>
       <c r="B96" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D96" s="16" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="E96" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F96" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G96" s="13"/>
       <c r="H96" s="13"/>
@@ -5735,19 +5833,19 @@
         <v>50</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C97" s="16" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F97" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G97" s="13"/>
       <c r="H97" s="13"/>
@@ -5758,19 +5856,19 @@
         <v>50</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="D98" s="16" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E98" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F98" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G98" s="13"/>
       <c r="H98" s="13"/>
@@ -5781,19 +5879,19 @@
         <v>50</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D99" s="16" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E99" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F99" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G99" s="13"/>
       <c r="H99" s="13"/>
@@ -5804,19 +5902,19 @@
         <v>50</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C100" s="16" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D100" s="16" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E100" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F100" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G100" s="13"/>
       <c r="H100" s="13"/>
@@ -5827,19 +5925,19 @@
         <v>50</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C101" s="16" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D101" s="16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E101" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F101" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G101" s="13"/>
       <c r="H101" s="13"/>
@@ -5850,19 +5948,19 @@
         <v>50</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C102" s="16" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D102" s="16" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F102" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G102" s="13"/>
       <c r="H102" s="13"/>
@@ -5873,19 +5971,19 @@
         <v>50</v>
       </c>
       <c r="B103" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C103" s="16" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D103" s="16" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F103" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G103" s="13"/>
       <c r="H103" s="13"/>
@@ -5896,19 +5994,19 @@
         <v>50</v>
       </c>
       <c r="B104" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C104" s="16" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F104" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G104" s="13"/>
       <c r="H104" s="13"/>
@@ -5919,19 +6017,19 @@
         <v>50</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C105" s="16" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D105" s="16" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F105" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G105" s="13"/>
       <c r="H105" s="13"/>
@@ -5942,19 +6040,19 @@
         <v>50</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C106" s="16" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D106" s="16" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F106" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G106" s="13"/>
       <c r="H106" s="13"/>
@@ -5965,19 +6063,19 @@
         <v>50</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C107" s="16" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="D107" s="16" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F107" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G107" s="13"/>
       <c r="H107" s="13"/>
@@ -5988,19 +6086,19 @@
         <v>50</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D108" s="16" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F108" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G108" s="13"/>
       <c r="H108" s="13"/>
@@ -6011,19 +6109,19 @@
         <v>50</v>
       </c>
       <c r="B109" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C109" s="16" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D109" s="16" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F109" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G109" s="13"/>
       <c r="H109" s="13"/>
@@ -6034,19 +6132,19 @@
         <v>50</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D110" s="16" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="E110" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F110" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G110" s="13"/>
       <c r="H110" s="13"/>
@@ -6057,19 +6155,19 @@
         <v>50</v>
       </c>
       <c r="B111" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D111" s="16" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F111" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G111" s="13"/>
       <c r="H111" s="13"/>
@@ -6080,19 +6178,19 @@
         <v>50</v>
       </c>
       <c r="B112" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F112" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G112" s="13"/>
       <c r="H112" s="13"/>
@@ -6103,19 +6201,19 @@
         <v>50</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C113" s="16" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D113" s="16" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F113" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G113" s="13"/>
       <c r="H113" s="13"/>
@@ -6126,19 +6224,19 @@
         <v>50</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D114" s="16" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F114" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G114" s="13"/>
       <c r="H114" s="13"/>
@@ -6149,19 +6247,19 @@
         <v>50</v>
       </c>
       <c r="B115" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C115" s="16" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D115" s="16" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="E115" s="17" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F115" s="17" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G115" s="13"/>
       <c r="H115" s="13"/>
@@ -6172,19 +6270,19 @@
         <v>50</v>
       </c>
       <c r="B116" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C116" s="16" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D116" s="16" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F116" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G116" s="13"/>
       <c r="H116" s="13"/>
@@ -6195,19 +6293,19 @@
         <v>50</v>
       </c>
       <c r="B117" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C117" s="16" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F117" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G117" s="13"/>
       <c r="H117" s="13"/>
@@ -6218,19 +6316,19 @@
         <v>50</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D118" s="16" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="E118" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F118" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G118" s="13"/>
       <c r="H118" s="13"/>
@@ -6241,19 +6339,19 @@
         <v>50</v>
       </c>
       <c r="B119" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C119" s="16" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D119" s="16" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F119" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G119" s="13"/>
       <c r="H119" s="13"/>
@@ -6264,19 +6362,19 @@
         <v>50</v>
       </c>
       <c r="B120" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C120" s="16" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D120" s="16" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F120" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G120" s="13"/>
       <c r="H120" s="13"/>
@@ -6287,19 +6385,19 @@
         <v>50</v>
       </c>
       <c r="B121" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F121" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G121" s="13"/>
       <c r="H121" s="13"/>
@@ -6310,19 +6408,19 @@
         <v>50</v>
       </c>
       <c r="B122" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C122" s="16" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F122" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G122" s="13"/>
       <c r="H122" s="13"/>
@@ -6333,19 +6431,19 @@
         <v>50</v>
       </c>
       <c r="B123" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C123" s="16" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D123" s="16" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E123" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F123" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G123" s="13"/>
       <c r="H123" s="13"/>
@@ -6356,19 +6454,19 @@
         <v>50</v>
       </c>
       <c r="B124" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C124" s="16" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D124" s="16" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E124" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F124" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G124" s="13"/>
       <c r="H124" s="13"/>
@@ -6379,19 +6477,19 @@
         <v>50</v>
       </c>
       <c r="B125" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C125" s="16" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F125" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G125" s="13"/>
       <c r="H125" s="13"/>
@@ -6402,19 +6500,19 @@
         <v>50</v>
       </c>
       <c r="B126" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C126" s="16" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F126" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G126" s="13"/>
       <c r="H126" s="13"/>
@@ -6425,19 +6523,19 @@
         <v>50</v>
       </c>
       <c r="B127" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C127" s="16" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D127" s="16" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F127" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G127" s="13"/>
       <c r="H127" s="13"/>
@@ -6448,19 +6546,19 @@
         <v>50</v>
       </c>
       <c r="B128" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C128" s="16" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="E128" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F128" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G128" s="13"/>
       <c r="H128" s="13"/>
@@ -6471,19 +6569,19 @@
         <v>50</v>
       </c>
       <c r="B129" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C129" s="16" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="E129" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F129" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G129" s="13"/>
       <c r="H129" s="13"/>
@@ -6494,19 +6592,19 @@
         <v>50</v>
       </c>
       <c r="B130" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C130" s="16" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D130" s="16" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="E130" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F130" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G130" s="13"/>
       <c r="H130" s="13"/>
@@ -6517,19 +6615,19 @@
         <v>50</v>
       </c>
       <c r="B131" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C131" s="16" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="E131" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F131" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G131" s="13"/>
       <c r="H131" s="13"/>
@@ -6540,19 +6638,19 @@
         <v>50</v>
       </c>
       <c r="B132" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C132" s="16" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="E132" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F132" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G132" s="13"/>
       <c r="H132" s="13"/>
@@ -6563,19 +6661,19 @@
         <v>50</v>
       </c>
       <c r="B133" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C133" s="16" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D133" s="16" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="E133" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F133" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G133" s="13"/>
       <c r="H133" s="13"/>
@@ -6586,19 +6684,19 @@
         <v>50</v>
       </c>
       <c r="B134" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C134" s="16" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E134" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F134" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G134" s="13"/>
       <c r="H134" s="13"/>
@@ -6609,19 +6707,19 @@
         <v>50</v>
       </c>
       <c r="B135" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="E135" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F135" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G135" s="13"/>
       <c r="H135" s="13"/>
@@ -6632,19 +6730,19 @@
         <v>50</v>
       </c>
       <c r="B136" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="E136" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F136" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G136" s="13"/>
       <c r="H136" s="13"/>
@@ -6655,19 +6753,19 @@
         <v>50</v>
       </c>
       <c r="B137" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E137" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F137" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G137" s="13"/>
       <c r="H137" s="13"/>
@@ -6678,19 +6776,19 @@
         <v>50</v>
       </c>
       <c r="B138" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C138" s="16" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="D138" s="16" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E138" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F138" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G138" s="13"/>
       <c r="H138" s="13"/>
@@ -6701,19 +6799,19 @@
         <v>50</v>
       </c>
       <c r="B139" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="E139" s="17" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F139" s="17" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="G139" s="13"/>
       <c r="H139" s="13"/>
@@ -6721,22 +6819,22 @@
     </row>
     <row r="140" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B140" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="E140" s="17" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F140" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G140" s="13"/>
       <c r="H140" s="13"/>
@@ -6744,22 +6842,22 @@
     </row>
     <row r="141" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B141" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C141" s="16" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="E141" s="17" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F141" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G141" s="13"/>
       <c r="H141" s="13"/>
@@ -6767,22 +6865,22 @@
     </row>
     <row r="142" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B142" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C142" s="16" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D142" s="16" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E142" s="17" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F142" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G142" s="13"/>
       <c r="H142" s="13"/>
@@ -6790,22 +6888,22 @@
     </row>
     <row r="143" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B143" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C143" s="16" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D143" s="16" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="E143" s="17" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F143" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G143" s="13"/>
       <c r="H143" s="13"/>
@@ -6813,22 +6911,22 @@
     </row>
     <row r="144" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B144" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C144" s="16" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="D144" s="16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E144" s="17" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F144" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G144" s="13"/>
       <c r="H144" s="13"/>
@@ -6836,22 +6934,22 @@
     </row>
     <row r="145" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B145" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C145" s="16" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D145" s="16" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="E145" s="17" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F145" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G145" s="13"/>
       <c r="H145" s="13"/>
@@ -6859,20 +6957,20 @@
     </row>
     <row r="146" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B146" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C146" s="16" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D146" s="16"/>
       <c r="E146" s="17" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F146" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G146" s="13"/>
       <c r="H146" s="13"/>
@@ -6880,22 +6978,22 @@
     </row>
     <row r="147" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B147" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C147" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="D147" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="E147" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="F147" s="17" t="s">
         <v>300</v>
-      </c>
-      <c r="D147" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="E147" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="F147" s="17" t="s">
-        <v>291</v>
       </c>
       <c r="G147" s="13"/>
       <c r="H147" s="13"/>
@@ -6903,22 +7001,22 @@
     </row>
     <row r="148" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B148" s="16" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="C148" s="16" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D148" s="16" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="E148" s="17" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F148" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G148" s="13"/>
       <c r="H148" s="13"/>
@@ -6926,22 +7024,22 @@
     </row>
     <row r="149" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B149" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C149" s="16" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D149" s="16" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="E149" s="17" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="F149" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G149" s="13"/>
       <c r="H149" s="13"/>
@@ -6949,22 +7047,22 @@
     </row>
     <row r="150" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B150" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C150" s="16" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D150" s="16" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E150" s="17" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="F150" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G150" s="13"/>
       <c r="H150" s="13"/>
@@ -6972,22 +7070,22 @@
     </row>
     <row r="151" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B151" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C151" s="16" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D151" s="16" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E151" s="17" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="F151" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G151" s="13"/>
       <c r="H151" s="13"/>
@@ -6995,22 +7093,22 @@
     </row>
     <row r="152" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B152" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C152" s="16" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D152" s="16" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="E152" s="17" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="F152" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G152" s="13"/>
       <c r="H152" s="13"/>
@@ -7018,22 +7116,22 @@
     </row>
     <row r="153" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B153" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C153" s="16" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="D153" s="16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E153" s="17" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="F153" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G153" s="13"/>
       <c r="H153" s="13"/>
@@ -7041,22 +7139,22 @@
     </row>
     <row r="154" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B154" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C154" s="16" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D154" s="16" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="E154" s="17" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="F154" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G154" s="13"/>
       <c r="H154" s="13"/>
@@ -7064,20 +7162,20 @@
     </row>
     <row r="155" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B155" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C155" s="16" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D155" s="16"/>
       <c r="E155" s="17" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="F155" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G155" s="13"/>
       <c r="H155" s="13"/>
@@ -7085,22 +7183,22 @@
     </row>
     <row r="156" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B156" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C156" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="D156" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="E156" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="F156" s="17" t="s">
         <v>300</v>
-      </c>
-      <c r="D156" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="E156" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="F156" s="17" t="s">
-        <v>291</v>
       </c>
       <c r="G156" s="13"/>
       <c r="H156" s="13"/>
@@ -7108,22 +7206,22 @@
     </row>
     <row r="157" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B157" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C157" s="16" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D157" s="16" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="E157" s="17" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="F157" s="17" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="G157" s="13"/>
       <c r="H157" s="13"/>
@@ -7131,22 +7229,22 @@
     </row>
     <row r="158" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B158" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C158" s="16" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D158" s="16" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E158" s="17" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="F158" s="17" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="G158" s="13"/>
       <c r="H158" s="13"/>
@@ -7154,22 +7252,22 @@
     </row>
     <row r="159" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B159" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C159" s="16" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D159" s="16" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E159" s="17" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="F159" s="17" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="G159" s="13"/>
       <c r="H159" s="13"/>
@@ -7177,22 +7275,22 @@
     </row>
     <row r="160" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B160" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C160" s="16" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D160" s="16" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E160" s="17" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="F160" s="17" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="G160" s="13"/>
       <c r="H160" s="13"/>
@@ -7200,22 +7298,22 @@
     </row>
     <row r="161" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B161" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C161" s="16" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D161" s="16" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="E161" s="17" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="F161" s="17" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="G161" s="13"/>
       <c r="H161" s="13"/>
@@ -7223,22 +7321,22 @@
     </row>
     <row r="162" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B162" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C162" s="16" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="D162" s="16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E162" s="17" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="F162" s="17" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="G162" s="13"/>
       <c r="H162" s="13"/>
@@ -7246,22 +7344,22 @@
     </row>
     <row r="163" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B163" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C163" s="16" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D163" s="16" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E163" s="17" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="F163" s="17" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="G163" s="13"/>
       <c r="H163" s="13"/>
@@ -7269,22 +7367,22 @@
     </row>
     <row r="164" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B164" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C164" s="16" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D164" s="16" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E164" s="17" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="F164" s="17" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="G164" s="13"/>
       <c r="H164" s="13"/>
@@ -7292,22 +7390,22 @@
     </row>
     <row r="165" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B165" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C165" s="16" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="D165" s="16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="E165" s="17" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="F165" s="17" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="G165" s="13"/>
       <c r="H165" s="13"/>
@@ -7315,22 +7413,22 @@
     </row>
     <row r="166" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="16" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B166" s="16" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C166" s="16" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D166" s="16" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="E166" s="17" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="F166" s="17" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="G166" s="13"/>
       <c r="H166" s="13"/>
@@ -7369,7 +7467,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -7384,32 +7482,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>35</v>
@@ -7423,10 +7521,10 @@
     </row>
     <row r="5" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>58</v>
@@ -7438,7 +7536,7 @@
         <v>60</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
@@ -7446,22 +7544,22 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>58</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>60</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
@@ -7469,10 +7567,10 @@
     </row>
     <row r="7" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>58</v>
@@ -7484,7 +7582,7 @@
         <v>60</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
@@ -7542,22 +7640,22 @@
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>60</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
@@ -7565,22 +7663,22 @@
     </row>
     <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E11" s="15" t="s">
         <v>60</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
@@ -7588,13 +7686,13 @@
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>64</v>
@@ -7603,7 +7701,7 @@
         <v>60</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
@@ -7611,22 +7709,22 @@
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>60</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
@@ -7634,13 +7732,13 @@
     </row>
     <row r="14" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>64</v>
@@ -7649,7 +7747,7 @@
         <v>60</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
@@ -7657,13 +7755,13 @@
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>64</v>
@@ -7672,13 +7770,13 @@
         <v>60</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
     </row>
-    <row r="16" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="191.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
         <v>66</v>
       </c>
@@ -7686,24 +7784,22 @@
         <v>67</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="E16" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>60</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="13" t="s">
-        <v>55</v>
-      </c>
+      <c r="G16" s="13"/>
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
     </row>
-    <row r="17" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
         <v>71</v>
       </c>
@@ -7711,24 +7807,22 @@
         <v>72</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="E17" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>60</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="G17" s="13" t="s">
-        <v>55</v>
-      </c>
+      <c r="G17" s="13"/>
       <c r="H17" s="13"/>
       <c r="I17" s="13"/>
     </row>
-    <row r="18" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
         <v>74</v>
       </c>
@@ -7736,150 +7830,216 @@
         <v>75</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-    </row>
-    <row r="19" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I18" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="D19" s="11" t="s">
         <v>77</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>69</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
+      <c r="I19" s="13" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-    </row>
-    <row r="21" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I20" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-    </row>
-    <row r="22" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I21" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-    </row>
-    <row r="23" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I22" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>60</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
+      <c r="I23" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13" t="s">
+        <v>82</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G5:G23">
+  <conditionalFormatting sqref="G5:G25">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Y"</formula>
     </cfRule>
@@ -7891,7 +8051,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Y if the loaded figure matches the source, N if it does not, Query if you could not find the document." errorStyle="stop" errorTitle="One of three answers" operator="between" prompt="Y, N or Query." promptTitle="Does the loaded value agree?" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G5:G23" type="list">
+    <dataValidation allowBlank="true" error="Y if the loaded figure matches the source, N if it does not, Query if you could not find the document." errorStyle="stop" errorTitle="One of three answers" operator="between" prompt="Y, N or Query." promptTitle="Does the loaded value agree?" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G5:G25" type="list">
       <formula1>"Y,N,Query"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7925,23 +8085,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>33</v>
@@ -7958,14 +8118,14 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -7973,14 +8133,14 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
@@ -7988,14 +8148,14 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
@@ -8003,14 +8163,14 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
@@ -8018,14 +8178,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
@@ -8033,14 +8193,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
@@ -8048,14 +8208,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
@@ -8063,16 +8223,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="13"/>
@@ -8080,14 +8240,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="13"/>
@@ -8095,14 +8255,14 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
@@ -8110,14 +8270,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="13"/>
@@ -8125,14 +8285,14 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="13"/>
@@ -8140,14 +8300,14 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E17" s="13"/>
       <c r="F17" s="13"/>
@@ -8155,16 +8315,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
@@ -8172,14 +8332,14 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
@@ -8187,14 +8347,14 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
@@ -8202,14 +8362,14 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="13"/>
@@ -8217,14 +8377,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
@@ -8232,14 +8392,14 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
@@ -8247,14 +8407,14 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="13"/>
@@ -8262,14 +8422,14 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
@@ -8277,14 +8437,14 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="13"/>
@@ -8292,14 +8452,14 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="13"/>
@@ -8307,16 +8467,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
@@ -8368,23 +8528,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>35</v>
@@ -8398,13 +8558,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="13"/>
@@ -8412,13 +8572,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>44</v>
@@ -8428,13 +8588,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="13"/>
@@ -8442,13 +8602,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D8" s="18" t="s">
         <v>44</v>
@@ -8458,13 +8618,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="13"/>
@@ -8472,13 +8632,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="13"/>
@@ -8486,13 +8646,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="B11" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>403</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>394</v>
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="13"/>
@@ -8500,13 +8660,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="13"/>
@@ -8514,13 +8674,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>44</v>
@@ -8530,13 +8690,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="D14" s="18"/>
       <c r="E14" s="13"/>
@@ -8544,13 +8704,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D15" s="18"/>
       <c r="E15" s="13"/>
@@ -8558,13 +8718,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>44</v>
@@ -8574,13 +8734,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="D17" s="18"/>
       <c r="E17" s="13"/>
@@ -8588,13 +8748,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="D18" s="18"/>
       <c r="E18" s="13"/>
@@ -8602,13 +8762,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B19" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>94</v>
       </c>
       <c r="D19" s="18" t="s">
         <v>44</v>
@@ -8618,13 +8778,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="D20" s="18"/>
       <c r="E20" s="13"/>
@@ -8632,13 +8792,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="13"/>
@@ -8646,13 +8806,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D22" s="18"/>
       <c r="E22" s="13"/>
@@ -8660,13 +8820,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="13"/>
@@ -8674,13 +8834,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="13"/>
@@ -8688,13 +8848,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D25" s="18" t="s">
         <v>44</v>
@@ -8704,13 +8864,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="D26" s="18"/>
       <c r="E26" s="13"/>
@@ -8718,13 +8878,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>44</v>
@@ -8734,13 +8894,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D28" s="18"/>
       <c r="E28" s="13"/>
@@ -8748,13 +8908,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="D29" s="18"/>
       <c r="E29" s="13"/>
@@ -8804,124 +8964,124 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -8940,7 +9100,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
@@ -8952,148 +9112,165 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C8" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>483</v>
       </c>
-      <c r="D8" s="18" t="s">
-        <v>474</v>
-      </c>
       <c r="E8" s="13" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>493</v>
+        <v>502</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>481</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>504</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>505</v>
       </c>
     </row>
   </sheetData>
